--- a/_fushi_modules/config/命运牌局_配置总表.xlsx
+++ b/_fushi_modules/config/命运牌局_配置总表.xlsx
@@ -11076,7 +11076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11154,6 +11154,16 @@
           <t>存放位置</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>养成属性</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>升级命尘</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -11212,6 +11222,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -11268,6 +11286,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -11324,6 +11350,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -11380,6 +11414,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -11435,6 +11477,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -11488,6 +11538,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -11544,6 +11602,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -11599,6 +11665,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -11652,6 +11726,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -11708,6 +11790,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -11764,6 +11854,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -11822,6 +11920,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -11878,6 +11984,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -11933,6 +12047,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -11986,6 +12108,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -12042,6 +12172,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -12098,6 +12236,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -12154,6 +12300,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -12212,6 +12366,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -12270,6 +12432,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -12328,6 +12498,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -12385,6 +12563,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="24">
@@ -12438,6 +12624,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12490,6 +12684,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -12542,6 +12744,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -12593,6 +12803,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="28">
@@ -12644,6 +12862,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -12703,6 +12929,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="30">
@@ -12756,6 +12990,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -12808,6 +13050,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -12864,6 +13114,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -12919,6 +13177,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="34">
@@ -12972,6 +13238,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -13024,6 +13298,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -13076,6 +13358,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -13133,6 +13423,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="38">
@@ -13186,6 +13484,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -13238,6 +13544,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -13290,6 +13604,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -13346,6 +13668,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -13402,6 +13732,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -13458,6 +13796,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -13514,6 +13860,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -13570,6 +13924,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -13626,6 +13988,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -13681,6 +14051,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>气血</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="48">
@@ -13734,6 +14112,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -13786,6 +14172,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -13838,6 +14232,14 @@
           <t>仓库解锁/传承台装备</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -13889,6 +14291,14 @@
         <is>
           <t>仓库解锁/传承台装备</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
